--- a/src/main/R/results-analysis_Siemensbahn-ohne-S21Jungfernheide-ausiterieren.xlsx
+++ b/src/main/R/results-analysis_Siemensbahn-ohne-S21Jungfernheide-ausiterieren.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eduardo Lima\Documents\TUB\Studium\Masterarbeit_git\matsim-berlin\src\main\R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{AE9FCC89-F9E5-43BE-AF00-4B139FEDA880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B6B7704-CB70-43EA-A81C-86BE65884118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4935" yWindow="-15870" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,26 +33,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={736561BD-4D1A-4791-81D1-0A00765B182F}</author>
-  </authors>
-  <commentList>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{736561BD-4D1A-4791-81D1-0A00765B182F}">
-      <text>
-        <t>[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
-    Total Travel Time in Car in Base Case for these Agents: 10.790 hours</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>Scenario</t>
   </si>
@@ -78,19 +60,28 @@
     <t>Siemensbahn</t>
   </si>
   <si>
+    <t>Diff to Base Case [EUR/day]</t>
+  </si>
+  <si>
+    <t>Total Travel Time in PT for Former Car-Users in Base Case [h/day]</t>
+  </si>
+  <si>
+    <t>Total Travel Time for Remaining PT-Users from Base Case [h/day]</t>
+  </si>
+  <si>
     <t>Siemensbahn+v1</t>
   </si>
   <si>
     <t>Siemensbahn+v2</t>
   </si>
   <si>
-    <t>Diff to Base Case [EUR/day]</t>
-  </si>
-  <si>
-    <t>Total Travel Time in PT for Former Car-Users in Base Case [h/day]</t>
-  </si>
-  <si>
-    <t>Total Travel Time for Remaining PT-Users from Base Case [h/day]</t>
+    <t>Diff to Base Case [1/day]</t>
+  </si>
+  <si>
+    <t>Diff to Base Case [km/day]</t>
+  </si>
+  <si>
+    <t>Diff to Base Case [h/day]</t>
   </si>
 </sst>
 </file>
@@ -118,19 +109,19 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Segoe UI"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -140,18 +131,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -183,10 +162,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -195,10 +174,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -214,12 +193,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Eduardo de Almeida Lima" id="{CA880B87-2CD4-432E-A584-C6664854B856}" userId="9a31f4cde4da338c" providerId="Windows Live"/>
-</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -507,23 +480,15 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="G3" dT="2025-08-28T11:41:42.92" personId="{CA880B87-2CD4-432E-A584-C6664854B856}" id="{736561BD-4D1A-4791-81D1-0A00765B182F}">
-    <text>Total Travel Time in Car in Base Case for these Agents: 10.790 hours</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="10" width="18.85546875" customWidth="1"/>
+    <col min="1" max="13" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="1" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -531,151 +496,195 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="4">
-        <v>576849472.08149779</v>
+        <v>577758076.27977991</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="4">
-        <v>27597046.524577219</v>
+        <v>21808131.968951229</v>
       </c>
       <c r="E2" s="5"/>
-      <c r="F2" s="8">
-        <v>277740.88555555558</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="6">
-        <v>267032</v>
-      </c>
+      <c r="F2" s="6">
+        <v>276979.04916666669</v>
+      </c>
+      <c r="G2" s="7">
+        <v>3254.73</v>
+      </c>
+      <c r="H2" s="8">
+        <v>270010.87599999999</v>
+      </c>
+      <c r="I2" s="5"/>
       <c r="J2" s="6">
-        <v>4432706.5199999996</v>
-      </c>
+        <v>266913</v>
+      </c>
+      <c r="K2" s="5"/>
+      <c r="L2" s="6">
+        <v>4514604.3449999997</v>
+      </c>
+      <c r="M2" s="5"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="4">
-        <v>576853479.88575673</v>
+        <v>577686297.25839734</v>
       </c>
       <c r="C3" s="4">
         <f>B3-B$2</f>
-        <v>4007.8042589426041</v>
+        <v>-71779.021382570267</v>
       </c>
       <c r="D3" s="4">
-        <v>27738560.02270747</v>
+        <v>21827838.550770171</v>
       </c>
       <c r="E3" s="4">
         <f>D3-D$2</f>
-        <v>141513.49813025072</v>
-      </c>
-      <c r="F3" s="7">
-        <v>277881.39694444451</v>
-      </c>
-      <c r="G3" s="7">
-        <v>10212</v>
-      </c>
-      <c r="H3" s="9">
-        <v>269152</v>
+        <v>19706.581818941981</v>
+      </c>
+      <c r="F3" s="6">
+        <v>277538.06416666659</v>
+      </c>
+      <c r="G3" s="6">
+        <v>5092.29</v>
+      </c>
+      <c r="H3" s="8">
+        <v>269962.625</v>
       </c>
       <c r="I3" s="6">
-        <v>266906</v>
+        <f>H3-H$2</f>
+        <v>-48.25099999998929</v>
       </c>
       <c r="J3" s="6">
-        <v>4428922.84</v>
+        <v>266953</v>
+      </c>
+      <c r="K3" s="6">
+        <f>J3-J$2</f>
+        <v>40</v>
+      </c>
+      <c r="L3" s="6">
+        <v>4508901.7149999999</v>
+      </c>
+      <c r="M3" s="6">
+        <f>L3-L$2</f>
+        <v>-5702.6299999998882</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4" s="4">
-        <v>577042817.95583272</v>
+        <v>577792258.83604789</v>
       </c>
       <c r="C4" s="4">
         <f>B4-B$2</f>
-        <v>193345.87433493137</v>
+        <v>34182.556267976761</v>
       </c>
       <c r="D4" s="4">
-        <v>27915089.280400202</v>
+        <v>21847699.318542141</v>
       </c>
       <c r="E4" s="4">
-        <f t="shared" ref="C4:E5" si="0">D4-D$2</f>
-        <v>318042.75582298264</v>
+        <f>D4-D$2</f>
+        <v>39567.349590912461</v>
       </c>
       <c r="F4" s="6">
-        <v>277436.07861111109</v>
+        <v>277636.7913888889</v>
       </c>
       <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6">
-        <v>265978</v>
-      </c>
+      <c r="H4" s="8"/>
+      <c r="I4" s="6"/>
       <c r="J4" s="6">
-        <v>4435347.9989999998</v>
+        <v>266886</v>
+      </c>
+      <c r="K4" s="6">
+        <f t="shared" ref="K4:M5" si="0">J4-J$2</f>
+        <v>-27</v>
+      </c>
+      <c r="L4" s="6">
+        <v>4507408.8650000002</v>
+      </c>
+      <c r="M4" s="6">
+        <f t="shared" si="0"/>
+        <v>-7195.4799999995157</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B5" s="4">
-        <v>576954629.6421262</v>
+        <v>577830827.14625168</v>
       </c>
       <c r="C5" s="4">
+        <f>B5-B$2</f>
+        <v>72750.866471767426</v>
+      </c>
+      <c r="D5" s="4">
+        <v>21844314.12200892</v>
+      </c>
+      <c r="E5" s="4">
+        <f>D5-D$2</f>
+        <v>36182.15305769071</v>
+      </c>
+      <c r="F5" s="6">
+        <v>277445.63194444438</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6">
+        <v>266531</v>
+      </c>
+      <c r="K5" s="6">
         <f t="shared" si="0"/>
-        <v>105157.56062841415</v>
-      </c>
-      <c r="D5" s="4">
-        <v>27805258.965537291</v>
-      </c>
-      <c r="E5" s="4">
+        <v>-382</v>
+      </c>
+      <c r="L5" s="6">
+        <v>4513263.7960000001</v>
+      </c>
+      <c r="M5" s="6">
         <f t="shared" si="0"/>
-        <v>208212.44096007198</v>
-      </c>
-      <c r="F5" s="6">
-        <v>277845.82666666672</v>
-      </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6">
-        <v>266274</v>
-      </c>
-      <c r="J5" s="6">
-        <v>4437178.284</v>
+        <v>-1340.5489999996498</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>